--- a/DADOSTESTE.xlsx
+++ b/DADOSTESTE.xlsx
@@ -487,6 +487,9 @@
       <c r="H2" s="1">
         <v>45728</v>
       </c>
+      <c r="I2" t="str">
+        <v>12/05/2026</v>
+      </c>
       <c r="J2" s="1">
         <v>45585</v>
       </c>
@@ -501,6 +504,9 @@
       </c>
       <c r="P2" t="str">
         <v>11/02/2036</v>
+      </c>
+      <c r="S2" t="str">
+        <v>15/02/2026</v>
       </c>
     </row>
     <row r="3">
@@ -578,8 +584,8 @@
       <c r="L4" s="1">
         <v>45546</v>
       </c>
-      <c r="M4" s="1">
-        <v>45791</v>
+      <c r="M4" t="str">
+        <v>14/05/2025</v>
       </c>
       <c r="P4" t="str">
         <v>03/01/2035</v>
